--- a/consent_forms/024_tv_series_release_form--consent_forms.xlsx
+++ b/consent_forms/024_tv_series_release_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'undetermined',_'label':_'undetermined'}</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Undetermined', 'label': 'Undetermined'}</t>
+          <t>Undetermined</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'cast',_'label':_'cast'}</t>
+          <t>cast</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Cast', 'label': 'Cast'}</t>
+          <t>Cast</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'contributor',_'label':_'contributor'}</t>
+          <t>contributor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Contributor', 'label': 'Contributor'}</t>
+          <t>Contributor</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'on-location',_'label':_'on-location'}</t>
+          <t>on-location</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'On-Location', 'label': 'On-Location'}</t>
+          <t>On-Location</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'film',_'label':_'film'}</t>
+          <t>film</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Film', 'label': 'Film'}</t>
+          <t>Film</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'tv',_'label':_'tv'}</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'TV', 'label': 'TV'}</t>
+          <t>TV</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'print',_'label':_'print'}</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Print', 'label': 'Print'}</t>
+          <t>Print</t>
         </is>
       </c>
     </row>
